--- a/utils/Tools/excel/12_item_道具.xlsx
+++ b/utils/Tools/excel/12_item_道具.xlsx
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
   <si>
     <t>道具id</t>
   </si>
@@ -176,10 +176,7 @@
     <t>[]{int id;int num}</t>
   </si>
   <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>c</t>
+    <t>cs</t>
   </si>
   <si>
     <t>金币</t>
@@ -414,12 +411,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1514,7 +1511,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>19</v>
@@ -1540,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
@@ -1556,13 +1553,13 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -1578,13 +1575,13 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
@@ -1606,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
@@ -1628,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
@@ -1650,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
@@ -1674,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -1689,7 +1686,7 @@
         <v>10</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1700,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
@@ -1715,7 +1712,7 @@
         <v>1000</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1726,7 +1723,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" s="2">
         <v>3</v>
@@ -1750,7 +1747,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14" s="2">
         <v>3</v>
@@ -1774,7 +1771,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" s="2">
         <v>3</v>
@@ -1798,7 +1795,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -1822,7 +1819,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -1846,7 +1843,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D18" s="2">
         <v>2</v>
@@ -1870,7 +1867,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D19" s="2">
         <v>2</v>
@@ -1894,7 +1891,7 @@
         <v>4</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D20" s="2">
         <v>2</v>
@@ -1918,7 +1915,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D21" s="2">
         <v>2</v>
@@ -1942,7 +1939,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D22" s="2">
         <v>4</v>
@@ -1957,7 +1954,7 @@
         <v>1000</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
